--- a/InputData/indst/IFStFS/Indst Fuels Subject to Fuel Shifting.xlsx
+++ b/InputData/indst/IFStFS/Indst Fuels Subject to Fuel Shifting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\indst\IFStFS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\indst\IFStFS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0759892E-1323-4FFF-9486-B98EF23171D2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A3EA26-E999-4158-8CD0-D8488CBB5D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31350" yWindow="4560" windowWidth="22830" windowHeight="17235" xr2:uid="{CEBBDD15-8244-44C2-A2EB-EB506D69E415}"/>
+    <workbookView xWindow="24390" yWindow="690" windowWidth="21690" windowHeight="18975" xr2:uid="{CEBBDD15-8244-44C2-A2EB-EB506D69E415}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>IFStFS Industrial Fuels Subject to Fuel Shifting</t>
   </si>
@@ -46,21 +46,6 @@
     <t>None needed</t>
   </si>
   <si>
-    <t>This variable specifies which fuel types are affected by the Industrial</t>
-  </si>
-  <si>
-    <t>Fuel Shifting policy lever.  As this data file is effectively part of a user-set</t>
-  </si>
-  <si>
-    <t>policy, no data source is needed.</t>
-  </si>
-  <si>
-    <t>Generally, fossil fuels should be flagged for shifting, while decarbonized</t>
-  </si>
-  <si>
-    <t>fuels such as electricity and hydrogen should not be flagged for shifting.</t>
-  </si>
-  <si>
     <t>This variable is a Boolean.</t>
   </si>
   <si>
@@ -152,12 +137,6 @@
   </si>
   <si>
     <t>construction 41T43</t>
-  </si>
-  <si>
-    <t>not in an input data file.</t>
-  </si>
-  <si>
-    <t>The "target" fuels shifted to are specified in policy lever settings,</t>
   </si>
   <si>
     <r>
@@ -216,7 +195,25 @@
     <t>LPG propane or butane if</t>
   </si>
   <si>
-    <t>You may or may not wish to shift away from biomass or purchased heat.</t>
+    <t>This variable specifies which fuel types are affected by the industrial electrification and hydrogen shifting</t>
+  </si>
+  <si>
+    <t>policy levers.  As this data file is effectively part of a user-set policy, no data source is needed.</t>
+  </si>
+  <si>
+    <t>The "target" fuels shifted to are based on the policy levers used, not set in an input data file.</t>
+  </si>
+  <si>
+    <t>Electricity and hydrogen must not be flagged in this variable for shifting, or the electrification and hydrogen</t>
+  </si>
+  <si>
+    <t>Generally, fossil fuels should be flagged for shifting, while you may or may not wish to</t>
+  </si>
+  <si>
+    <t>flag biomass and purchased heat for shifting.</t>
+  </si>
+  <si>
+    <t>shifting levers will not work correctly in the model.  Leave electricity and hydrogen set to zero for all industries.</t>
   </si>
 </sst>
 </file>
@@ -248,7 +245,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,6 +255,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,10 +277,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -287,6 +289,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D74327C6-C2CB-4CD6-A944-44D7EC17E747}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -619,74 +625,69 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5</v>
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>39</v>
+      <c r="A12" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>7</v>
+      <c r="A13" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
+      <c r="A18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -707,46 +708,46 @@
     <col min="2" max="11" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>13</v>
+    <row r="1" spans="1:11" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="K1" s="7" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8">
         <v>0</v>
       </c>
       <c r="C2">
@@ -773,15 +774,15 @@
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8">
         <v>0</v>
       </c>
       <c r="C3">
@@ -808,15 +809,15 @@
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="B4" s="8">
         <v>0</v>
       </c>
       <c r="C4">
@@ -843,15 +844,15 @@
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="B5" s="8">
         <v>0</v>
       </c>
       <c r="C5">
@@ -878,15 +879,15 @@
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
+        <v>13</v>
+      </c>
+      <c r="B6" s="8">
         <v>0</v>
       </c>
       <c r="C6">
@@ -913,15 +914,15 @@
       <c r="J6">
         <v>1</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="B7" s="8">
         <v>0</v>
       </c>
       <c r="C7">
@@ -948,15 +949,15 @@
       <c r="J7">
         <v>1</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8">
+        <v>15</v>
+      </c>
+      <c r="B8" s="8">
         <v>0</v>
       </c>
       <c r="C8">
@@ -983,15 +984,15 @@
       <c r="J8">
         <v>1</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9">
+        <v>16</v>
+      </c>
+      <c r="B9" s="8">
         <v>0</v>
       </c>
       <c r="C9">
@@ -1018,15 +1019,15 @@
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10">
+        <v>17</v>
+      </c>
+      <c r="B10" s="8">
         <v>0</v>
       </c>
       <c r="C10">
@@ -1053,15 +1054,15 @@
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11">
+        <v>18</v>
+      </c>
+      <c r="B11" s="8">
         <v>0</v>
       </c>
       <c r="C11">
@@ -1088,15 +1089,15 @@
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12">
+        <v>19</v>
+      </c>
+      <c r="B12" s="8">
         <v>0</v>
       </c>
       <c r="C12">
@@ -1123,15 +1124,15 @@
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="B13" s="8">
         <v>0</v>
       </c>
       <c r="C13">
@@ -1158,15 +1159,15 @@
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14">
+        <v>21</v>
+      </c>
+      <c r="B14" s="8">
         <v>0</v>
       </c>
       <c r="C14">
@@ -1193,15 +1194,15 @@
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15">
+        <v>22</v>
+      </c>
+      <c r="B15" s="8">
         <v>0</v>
       </c>
       <c r="C15">
@@ -1228,15 +1229,15 @@
       <c r="J15">
         <v>1</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16">
+        <v>23</v>
+      </c>
+      <c r="B16" s="8">
         <v>0</v>
       </c>
       <c r="C16">
@@ -1263,15 +1264,15 @@
       <c r="J16">
         <v>1</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17">
+        <v>24</v>
+      </c>
+      <c r="B17" s="8">
         <v>0</v>
       </c>
       <c r="C17">
@@ -1298,15 +1299,15 @@
       <c r="J17">
         <v>1</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18">
+        <v>25</v>
+      </c>
+      <c r="B18" s="8">
         <v>0</v>
       </c>
       <c r="C18">
@@ -1333,15 +1334,15 @@
       <c r="J18">
         <v>1</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19">
+        <v>26</v>
+      </c>
+      <c r="B19" s="8">
         <v>0</v>
       </c>
       <c r="C19">
@@ -1368,15 +1369,15 @@
       <c r="J19">
         <v>1</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20">
+        <v>27</v>
+      </c>
+      <c r="B20" s="8">
         <v>0</v>
       </c>
       <c r="C20">
@@ -1403,15 +1404,15 @@
       <c r="J20">
         <v>1</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21">
+        <v>28</v>
+      </c>
+      <c r="B21" s="8">
         <v>0</v>
       </c>
       <c r="C21">
@@ -1438,15 +1439,15 @@
       <c r="J21">
         <v>1</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22">
+        <v>29</v>
+      </c>
+      <c r="B22" s="8">
         <v>0</v>
       </c>
       <c r="C22">
@@ -1473,15 +1474,15 @@
       <c r="J22">
         <v>1</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23">
+        <v>30</v>
+      </c>
+      <c r="B23" s="8">
         <v>0</v>
       </c>
       <c r="C23">
@@ -1508,15 +1509,15 @@
       <c r="J23">
         <v>1</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24">
+        <v>31</v>
+      </c>
+      <c r="B24" s="8">
         <v>0</v>
       </c>
       <c r="C24">
@@ -1543,15 +1544,15 @@
       <c r="J24">
         <v>1</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25">
+        <v>32</v>
+      </c>
+      <c r="B25" s="8">
         <v>0</v>
       </c>
       <c r="C25">
@@ -1578,15 +1579,15 @@
       <c r="J25">
         <v>1</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26">
+        <v>33</v>
+      </c>
+      <c r="B26" s="8">
         <v>0</v>
       </c>
       <c r="C26">
@@ -1613,11 +1614,182 @@
       <c r="J26">
         <v>1</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d97e5666cdfcf1fb012d61a0a672e358">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9a863ab7d701f66181e0031a8bef47d7" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2B7F1CE-F36E-422C-A7D7-3EC397147364}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C551EC0E-22E7-4EC9-A935-515B7BE2640D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53F11AE3-8FB6-4897-8DBC-9B4906224B72}"/>
 </file>